--- a/九龙-启德-Double Coast III/Double Coast III_销控明细表.xlsx
+++ b/九龙-启德-Double Coast III/Double Coast III_销控明细表.xlsx
@@ -1061,7 +1061,7 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="H7" s="5" t="n">
@@ -3627,7 +3627,7 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="H44" s="5" t="n">
@@ -4039,7 +4039,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="H50" s="5" t="n">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="H54" s="5" t="n">
@@ -4443,7 +4443,7 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="H56" s="5" t="n">
@@ -4505,7 +4505,7 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="H57" s="5" t="n">
@@ -5259,7 +5259,7 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="H68" s="5" t="n">
@@ -5321,7 +5321,7 @@
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="H69" s="5" t="n">
@@ -5655,7 +5655,7 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="H74" s="5" t="n">
@@ -5717,7 +5717,7 @@
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="H75" s="5" t="n">
@@ -5919,7 +5919,7 @@
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="H78" s="5" t="n">
@@ -6051,7 +6051,7 @@
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="H80" s="5" t="n">
@@ -6113,7 +6113,7 @@
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="H81" s="5" t="n">
@@ -6455,7 +6455,7 @@
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="H86" s="5" t="n">
@@ -6517,7 +6517,7 @@
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="H87" s="5" t="n">
@@ -6719,7 +6719,7 @@
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="H90" s="5" t="n">
@@ -6851,7 +6851,7 @@
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="H92" s="5" t="n">
@@ -6913,7 +6913,7 @@
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="H93" s="5" t="n">
@@ -7115,7 +7115,7 @@
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="H96" s="5" t="n">
@@ -7247,7 +7247,7 @@
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="H98" s="5" t="n">
@@ -7309,7 +7309,7 @@
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="H99" s="5" t="n">
@@ -7511,7 +7511,7 @@
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="H102" s="5" t="n">
@@ -7573,7 +7573,7 @@
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="H103" s="5" t="n">
@@ -7635,7 +7635,7 @@
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="H104" s="5" t="n">
@@ -7697,7 +7697,7 @@
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="H105" s="5" t="n">
@@ -7899,7 +7899,7 @@
       </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="H108" s="5" t="n">
@@ -7961,7 +7961,7 @@
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="H109" s="5" t="n">
@@ -8023,7 +8023,7 @@
       </c>
       <c r="G110" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="H110" s="5" t="n">
@@ -8085,7 +8085,7 @@
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="H111" s="5" t="n">
@@ -8287,7 +8287,7 @@
       </c>
       <c r="G114" s="3" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="H114" s="5" t="n">
@@ -8349,7 +8349,7 @@
       </c>
       <c r="G115" s="3" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="H115" s="5" t="n">
@@ -8411,7 +8411,7 @@
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="H116" s="5" t="n">
@@ -8473,7 +8473,7 @@
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="H117" s="5" t="n">
@@ -8675,7 +8675,7 @@
       </c>
       <c r="G120" s="3" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="H120" s="5" t="n">
@@ -8737,7 +8737,7 @@
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="H121" s="5" t="n">
@@ -8799,7 +8799,7 @@
       </c>
       <c r="G122" s="3" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="H122" s="5" t="n">
@@ -8861,7 +8861,7 @@
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="H123" s="5" t="n">
@@ -9063,7 +9063,7 @@
       </c>
       <c r="G126" s="3" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="H126" s="5" t="n">
@@ -9125,7 +9125,7 @@
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="H127" s="5" t="n">
@@ -9187,7 +9187,7 @@
       </c>
       <c r="G128" s="3" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="H128" s="5" t="n">
@@ -9249,7 +9249,7 @@
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="H129" s="5" t="n">
@@ -9451,7 +9451,7 @@
       </c>
       <c r="G132" s="3" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="H132" s="5" t="n">
@@ -9513,7 +9513,7 @@
       </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="H133" s="5" t="n">
@@ -9575,7 +9575,7 @@
       </c>
       <c r="G134" s="3" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="H134" s="5" t="n">
@@ -9637,7 +9637,7 @@
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="H135" s="5" t="n">
@@ -9839,7 +9839,7 @@
       </c>
       <c r="G138" s="3" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="H138" s="5" t="n">
@@ -9901,7 +9901,7 @@
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="H139" s="5" t="n">
@@ -9963,7 +9963,7 @@
       </c>
       <c r="G140" s="3" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="H140" s="5" t="n">
@@ -10025,7 +10025,7 @@
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="H141" s="5" t="n">
@@ -10227,7 +10227,7 @@
       </c>
       <c r="G144" s="3" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="H144" s="5" t="n">
@@ -10289,7 +10289,7 @@
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="H145" s="5" t="n">
@@ -10351,7 +10351,7 @@
       </c>
       <c r="G146" s="3" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="H146" s="5" t="n">
@@ -10413,7 +10413,7 @@
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="H147" s="5" t="n">
@@ -10615,7 +10615,7 @@
       </c>
       <c r="G150" s="3" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="H150" s="5" t="n">
@@ -10677,7 +10677,7 @@
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="H151" s="5" t="n">
@@ -10739,7 +10739,7 @@
       </c>
       <c r="G152" s="3" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="H152" s="5" t="n">
@@ -10801,7 +10801,7 @@
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
-          <t>2026-01-11</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="H153" s="5" t="n">
@@ -11003,7 +11003,7 @@
       </c>
       <c r="G156" s="3" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="H156" s="5" t="n">
@@ -11065,7 +11065,7 @@
       </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="H157" s="5" t="n">
@@ -11127,7 +11127,7 @@
       </c>
       <c r="G158" s="3" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="H158" s="5" t="n">
@@ -11189,7 +11189,7 @@
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="H159" s="5" t="n">
@@ -11391,7 +11391,7 @@
       </c>
       <c r="G162" s="3" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="H162" s="5" t="n">
@@ -11453,7 +11453,7 @@
       </c>
       <c r="G163" s="3" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="H163" s="5" t="n">
@@ -11515,7 +11515,7 @@
       </c>
       <c r="G164" s="3" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="H164" s="5" t="n">
@@ -11577,7 +11577,7 @@
       </c>
       <c r="G165" s="3" t="inlineStr">
         <is>
-          <t>2026-01-11</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="H165" s="5" t="n">
@@ -11779,7 +11779,7 @@
       </c>
       <c r="G168" s="3" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="H168" s="5" t="n">
@@ -11841,7 +11841,7 @@
       </c>
       <c r="G169" s="3" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="H169" s="5" t="n">
@@ -11903,7 +11903,7 @@
       </c>
       <c r="G170" s="3" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="H170" s="5" t="n">
@@ -11965,7 +11965,7 @@
       </c>
       <c r="G171" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="H171" s="5" t="n">
@@ -12167,7 +12167,7 @@
       </c>
       <c r="G174" s="3" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H174" s="5" t="n">
@@ -12299,7 +12299,7 @@
       </c>
       <c r="G176" s="3" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="H176" s="5" t="n">
@@ -12361,7 +12361,7 @@
       </c>
       <c r="G177" s="3" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="H177" s="5" t="n">
@@ -16125,7 +16125,7 @@
       </c>
       <c r="G231" s="3" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="H231" s="5" t="n">
@@ -16187,7 +16187,7 @@
       </c>
       <c r="G232" s="3" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="H232" s="5" t="n">
@@ -16249,7 +16249,7 @@
       </c>
       <c r="G233" s="3" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="H233" s="5" t="n">
@@ -16381,7 +16381,7 @@
       </c>
       <c r="G235" s="3" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="H235" s="5" t="n">
@@ -16653,7 +16653,7 @@
       </c>
       <c r="G239" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="H239" s="5" t="n">
@@ -16785,7 +16785,7 @@
       </c>
       <c r="G241" s="3" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="H241" s="5" t="n">
@@ -16847,7 +16847,7 @@
       </c>
       <c r="G242" s="3" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="H242" s="5" t="n">
@@ -16909,7 +16909,7 @@
       </c>
       <c r="G243" s="3" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="H243" s="5" t="n">
@@ -17041,7 +17041,7 @@
       </c>
       <c r="G245" s="3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="H245" s="5" t="n">
@@ -17313,7 +17313,7 @@
       </c>
       <c r="G249" s="3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="H249" s="5" t="n">
@@ -17445,7 +17445,7 @@
       </c>
       <c r="G251" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="H251" s="5" t="n">
@@ -17507,7 +17507,7 @@
       </c>
       <c r="G252" s="3" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="H252" s="5" t="n">
@@ -17569,7 +17569,7 @@
       </c>
       <c r="G253" s="3" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="H253" s="5" t="n">
@@ -17701,7 +17701,7 @@
       </c>
       <c r="G255" s="3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="H255" s="5" t="n">
@@ -17973,7 +17973,7 @@
       </c>
       <c r="G259" s="3" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="H259" s="5" t="n">
@@ -18105,7 +18105,7 @@
       </c>
       <c r="G261" s="3" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="H261" s="5" t="n">
@@ -18167,7 +18167,7 @@
       </c>
       <c r="G262" s="3" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="H262" s="5" t="n">
@@ -18229,7 +18229,7 @@
       </c>
       <c r="G263" s="3" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="H263" s="5" t="n">
@@ -18361,7 +18361,7 @@
       </c>
       <c r="G265" s="3" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="H265" s="5" t="n">
@@ -18633,7 +18633,7 @@
       </c>
       <c r="G269" s="3" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="H269" s="5" t="n">
@@ -18765,7 +18765,7 @@
       </c>
       <c r="G271" s="3" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="H271" s="5" t="n">
@@ -18827,7 +18827,7 @@
       </c>
       <c r="G272" s="3" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="H272" s="5" t="n">
@@ -18889,7 +18889,7 @@
       </c>
       <c r="G273" s="3" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="H273" s="5" t="n">
@@ -19021,7 +19021,7 @@
       </c>
       <c r="G275" s="3" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="H275" s="5" t="n">
@@ -19293,7 +19293,7 @@
       </c>
       <c r="G279" s="3" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="H279" s="5" t="n">
@@ -19425,7 +19425,7 @@
       </c>
       <c r="G281" s="3" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="H281" s="5" t="n">
@@ -19487,7 +19487,7 @@
       </c>
       <c r="G282" s="3" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="H282" s="5" t="n">
@@ -19549,7 +19549,7 @@
       </c>
       <c r="G283" s="3" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="H283" s="5" t="n">
@@ -19681,7 +19681,7 @@
       </c>
       <c r="G285" s="3" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="H285" s="5" t="n">
@@ -19953,7 +19953,7 @@
       </c>
       <c r="G289" s="3" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="H289" s="5" t="n">
@@ -20085,7 +20085,7 @@
       </c>
       <c r="G291" s="3" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="H291" s="5" t="n">
@@ -20147,7 +20147,7 @@
       </c>
       <c r="G292" s="3" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="H292" s="5" t="n">
@@ -20209,7 +20209,7 @@
       </c>
       <c r="G293" s="3" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="H293" s="5" t="n">
@@ -20341,7 +20341,7 @@
       </c>
       <c r="G295" s="3" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="H295" s="5" t="n">
@@ -20403,7 +20403,7 @@
       </c>
       <c r="G296" s="3" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="H296" s="5" t="n">
@@ -21305,7 +21305,7 @@
       </c>
       <c r="G309" s="3" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="H309" s="5" t="n">
@@ -21437,7 +21437,7 @@
       </c>
       <c r="G311" s="3" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="H311" s="5" t="n">
@@ -21499,7 +21499,7 @@
       </c>
       <c r="G312" s="3" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="H312" s="5" t="n">
@@ -21561,7 +21561,7 @@
       </c>
       <c r="G313" s="3" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="H313" s="5" t="n">
@@ -21693,7 +21693,7 @@
       </c>
       <c r="G315" s="3" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="H315" s="5" t="n">
@@ -21755,7 +21755,7 @@
       </c>
       <c r="G316" s="3" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="H316" s="5" t="n">
@@ -21957,7 +21957,7 @@
       </c>
       <c r="G319" s="3" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="H319" s="5" t="n">
@@ -22089,7 +22089,7 @@
       </c>
       <c r="G321" s="3" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="H321" s="5" t="n">
@@ -22151,7 +22151,7 @@
       </c>
       <c r="G322" s="3" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="H322" s="5" t="n">
@@ -22213,7 +22213,7 @@
       </c>
       <c r="G323" s="3" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="H323" s="5" t="n">
@@ -22345,7 +22345,7 @@
       </c>
       <c r="G325" s="3" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="H325" s="5" t="n">
@@ -22407,7 +22407,7 @@
       </c>
       <c r="G326" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="H326" s="5" t="n">
@@ -22609,7 +22609,7 @@
       </c>
       <c r="G329" s="3" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="H329" s="5" t="n">
@@ -22741,7 +22741,7 @@
       </c>
       <c r="G331" s="3" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="H331" s="5" t="n">
@@ -22803,7 +22803,7 @@
       </c>
       <c r="G332" s="3" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="H332" s="5" t="n">
@@ -22865,7 +22865,7 @@
       </c>
       <c r="G333" s="3" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="H333" s="5" t="n">
@@ -22997,7 +22997,7 @@
       </c>
       <c r="G335" s="3" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="H335" s="5" t="n">
@@ -23059,7 +23059,7 @@
       </c>
       <c r="G336" s="3" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="H336" s="5" t="n">
@@ -23261,7 +23261,7 @@
       </c>
       <c r="G339" s="3" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="H339" s="5" t="n">
@@ -23393,7 +23393,7 @@
       </c>
       <c r="G341" s="3" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="H341" s="5" t="n">
@@ -23455,7 +23455,7 @@
       </c>
       <c r="G342" s="3" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="H342" s="5" t="n">
@@ -23517,7 +23517,7 @@
       </c>
       <c r="G343" s="3" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="H343" s="5" t="n">
@@ -23649,7 +23649,7 @@
       </c>
       <c r="G345" s="3" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="H345" s="5" t="n">
@@ -23711,7 +23711,7 @@
       </c>
       <c r="G346" s="3" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="H346" s="5" t="n">
@@ -23913,7 +23913,7 @@
       </c>
       <c r="G349" s="3" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="H349" s="5" t="n">
@@ -24045,7 +24045,7 @@
       </c>
       <c r="G351" s="3" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="H351" s="5" t="n">
@@ -24107,7 +24107,7 @@
       </c>
       <c r="G352" s="3" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="H352" s="5" t="n">
@@ -24169,7 +24169,7 @@
       </c>
       <c r="G353" s="3" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="H353" s="5" t="n">
@@ -24301,7 +24301,7 @@
       </c>
       <c r="G355" s="3" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="H355" s="5" t="n">
@@ -24363,7 +24363,7 @@
       </c>
       <c r="G356" s="3" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="H356" s="5" t="n">
@@ -24565,7 +24565,7 @@
       </c>
       <c r="G359" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="H359" s="5" t="n">
@@ -24697,7 +24697,7 @@
       </c>
       <c r="G361" s="3" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="H361" s="5" t="n">
@@ -24759,7 +24759,7 @@
       </c>
       <c r="G362" s="3" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="H362" s="5" t="n">
@@ -24821,7 +24821,7 @@
       </c>
       <c r="G363" s="3" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="H363" s="5" t="n">
@@ -24953,7 +24953,7 @@
       </c>
       <c r="G365" s="3" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="H365" s="5" t="n">
@@ -25015,7 +25015,7 @@
       </c>
       <c r="G366" s="3" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="H366" s="5" t="n">
@@ -25217,7 +25217,7 @@
       </c>
       <c r="G369" s="3" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="H369" s="5" t="n">
@@ -25349,7 +25349,7 @@
       </c>
       <c r="G371" s="3" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="H371" s="5" t="n">
@@ -25411,7 +25411,7 @@
       </c>
       <c r="G372" s="3" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="H372" s="5" t="n">
@@ -25473,7 +25473,7 @@
       </c>
       <c r="G373" s="3" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="H373" s="5" t="n">
@@ -25605,7 +25605,7 @@
       </c>
       <c r="G375" s="3" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="H375" s="5" t="n">
@@ -25667,7 +25667,7 @@
       </c>
       <c r="G376" s="3" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="H376" s="5" t="n">
@@ -25869,7 +25869,7 @@
       </c>
       <c r="G379" s="3" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="H379" s="5" t="n">
@@ -26001,7 +26001,7 @@
       </c>
       <c r="G381" s="3" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="H381" s="5" t="n">
@@ -26063,7 +26063,7 @@
       </c>
       <c r="G382" s="3" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="H382" s="5" t="n">
@@ -26125,7 +26125,7 @@
       </c>
       <c r="G383" s="3" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="H383" s="5" t="n">
@@ -26257,7 +26257,7 @@
       </c>
       <c r="G385" s="3" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="H385" s="5" t="n">
@@ -26319,7 +26319,7 @@
       </c>
       <c r="G386" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="H386" s="5" t="n">
@@ -26521,7 +26521,7 @@
       </c>
       <c r="G389" s="3" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="H389" s="5" t="n">
@@ -26653,7 +26653,7 @@
       </c>
       <c r="G391" s="3" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="H391" s="5" t="n">
@@ -26715,7 +26715,7 @@
       </c>
       <c r="G392" s="3" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="H392" s="5" t="n">
@@ -26777,7 +26777,7 @@
       </c>
       <c r="G393" s="3" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="H393" s="5" t="n">
@@ -26909,7 +26909,7 @@
       </c>
       <c r="G395" s="3" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="H395" s="5" t="n">
@@ -26971,7 +26971,7 @@
       </c>
       <c r="G396" s="3" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="H396" s="5" t="n">
@@ -27173,7 +27173,7 @@
       </c>
       <c r="G399" s="3" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="H399" s="5" t="n">
@@ -27305,7 +27305,7 @@
       </c>
       <c r="G401" s="3" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="H401" s="5" t="n">
@@ -27367,7 +27367,7 @@
       </c>
       <c r="G402" s="3" t="inlineStr">
         <is>
-          <t>2026-02-15</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="H402" s="5" t="n">
@@ -27429,7 +27429,7 @@
       </c>
       <c r="G403" s="3" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="H403" s="5" t="n">
@@ -27561,7 +27561,7 @@
       </c>
       <c r="G405" s="3" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="H405" s="5" t="n">
@@ -27623,7 +27623,7 @@
       </c>
       <c r="G406" s="3" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="H406" s="5" t="n">
@@ -27825,7 +27825,7 @@
       </c>
       <c r="G409" s="3" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="H409" s="5" t="n">
@@ -27957,7 +27957,7 @@
       </c>
       <c r="G411" s="3" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="H411" s="5" t="n">
@@ -28019,7 +28019,7 @@
       </c>
       <c r="G412" s="3" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="H412" s="5" t="n">
@@ -28081,7 +28081,7 @@
       </c>
       <c r="G413" s="3" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="H413" s="5" t="n">
@@ -28213,7 +28213,7 @@
       </c>
       <c r="G415" s="3" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="H415" s="5" t="n">
@@ -28275,7 +28275,7 @@
       </c>
       <c r="G416" s="3" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="H416" s="5" t="n">
@@ -28477,7 +28477,7 @@
       </c>
       <c r="G419" s="3" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="H419" s="5" t="n">
@@ -28609,7 +28609,7 @@
       </c>
       <c r="G421" s="3" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="H421" s="5" t="n">
@@ -28671,7 +28671,7 @@
       </c>
       <c r="G422" s="3" t="inlineStr">
         <is>
-          <t>2026-01-25</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="H422" s="5" t="n">
@@ -28733,7 +28733,7 @@
       </c>
       <c r="G423" s="3" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="H423" s="5" t="n">
@@ -28865,7 +28865,7 @@
       </c>
       <c r="G425" s="3" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="H425" s="5" t="n">
@@ -28927,7 +28927,7 @@
       </c>
       <c r="G426" s="3" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="H426" s="5" t="n">
@@ -29129,7 +29129,7 @@
       </c>
       <c r="G429" s="3" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="H429" s="5" t="n">
@@ -29261,7 +29261,7 @@
       </c>
       <c r="G431" s="3" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="H431" s="5" t="n">
@@ -29323,7 +29323,7 @@
       </c>
       <c r="G432" s="3" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="H432" s="5" t="n">
@@ -29385,7 +29385,7 @@
       </c>
       <c r="G433" s="3" t="inlineStr">
         <is>
-          <t>2026-01-11</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="H433" s="5" t="n">
@@ -29517,7 +29517,7 @@
       </c>
       <c r="G435" s="3" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="H435" s="5" t="n">
@@ -29579,7 +29579,7 @@
       </c>
       <c r="G436" s="3" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="H436" s="5" t="n">
@@ -29781,7 +29781,7 @@
       </c>
       <c r="G439" s="3" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="H439" s="5" t="n">
@@ -29913,7 +29913,7 @@
       </c>
       <c r="G441" s="3" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="H441" s="5" t="n">
@@ -29975,7 +29975,7 @@
       </c>
       <c r="G442" s="3" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="H442" s="5" t="n">
@@ -30037,7 +30037,7 @@
       </c>
       <c r="G443" s="3" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="H443" s="5" t="n">
@@ -30169,7 +30169,7 @@
       </c>
       <c r="G445" s="3" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="H445" s="5" t="n">
@@ -30231,7 +30231,7 @@
       </c>
       <c r="G446" s="3" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="H446" s="5" t="n">
@@ -30433,7 +30433,7 @@
       </c>
       <c r="G449" s="3" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="H449" s="5" t="n">
@@ -30565,7 +30565,7 @@
       </c>
       <c r="G451" s="3" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="H451" s="5" t="n">
@@ -30627,7 +30627,7 @@
       </c>
       <c r="G452" s="3" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="H452" s="5" t="n">
@@ -30689,7 +30689,7 @@
       </c>
       <c r="G453" s="3" t="inlineStr">
         <is>
-          <t>2026-01-18</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="H453" s="5" t="n">
@@ -30821,7 +30821,7 @@
       </c>
       <c r="G455" s="3" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="H455" s="5" t="n">
@@ -30883,7 +30883,7 @@
       </c>
       <c r="G456" s="3" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="H456" s="5" t="n">
@@ -31085,7 +31085,7 @@
       </c>
       <c r="G459" s="3" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
+          <t>2025-12-14</t>
         </is>
       </c>
       <c r="H459" s="5" t="n">
@@ -31217,7 +31217,7 @@
       </c>
       <c r="G461" s="3" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="H461" s="5" t="n">
@@ -31279,7 +31279,7 @@
       </c>
       <c r="G462" s="3" t="inlineStr">
         <is>
-          <t>2026-01-25</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="H462" s="5" t="n">
@@ -31341,7 +31341,7 @@
       </c>
       <c r="G463" s="3" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="H463" s="5" t="n">
@@ -31473,7 +31473,7 @@
       </c>
       <c r="G465" s="3" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="H465" s="5" t="n">
@@ -31535,7 +31535,7 @@
       </c>
       <c r="G466" s="3" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="H466" s="5" t="n">
@@ -31737,7 +31737,7 @@
       </c>
       <c r="G469" s="3" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="H469" s="5" t="n">
@@ -31869,7 +31869,7 @@
       </c>
       <c r="G471" s="3" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="H471" s="5" t="n">
@@ -31931,7 +31931,7 @@
       </c>
       <c r="G472" s="3" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="H472" s="5" t="n">
@@ -31993,7 +31993,7 @@
       </c>
       <c r="G473" s="3" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H473" s="5" t="n">
@@ -32125,7 +32125,7 @@
       </c>
       <c r="G475" s="3" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="H475" s="5" t="n">
@@ -32187,7 +32187,7 @@
       </c>
       <c r="G476" s="3" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="H476" s="5" t="n">
@@ -32389,7 +32389,7 @@
       </c>
       <c r="G479" s="3" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="H479" s="5" t="n">
@@ -32521,7 +32521,7 @@
       </c>
       <c r="G481" s="3" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="H481" s="5" t="n">
@@ -32583,7 +32583,7 @@
       </c>
       <c r="G482" s="3" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="H482" s="5" t="n">
@@ -32777,7 +32777,7 @@
       </c>
       <c r="G485" s="3" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="H485" s="5" t="n">
@@ -32839,7 +32839,7 @@
       </c>
       <c r="G486" s="3" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="H486" s="5" t="n">
@@ -33041,7 +33041,7 @@
       </c>
       <c r="G489" s="3" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="H489" s="5" t="n">
@@ -33173,7 +33173,7 @@
       </c>
       <c r="G491" s="3" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="H491" s="5" t="n">
@@ -33297,7 +33297,7 @@
       </c>
       <c r="G493" s="3" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="H493" s="5" t="n">
@@ -33429,7 +33429,7 @@
       </c>
       <c r="G495" s="3" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="H495" s="5" t="n">
@@ -33491,7 +33491,7 @@
       </c>
       <c r="G496" s="3" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="H496" s="5" t="n">
@@ -35838,7 +35838,7 @@
           <t>A | 1378呎 (4+房)
 $4668万
 $33,877/呎
-(26年-04月-07日)</t>
+(26年-04月-08日)</t>
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr"/>
@@ -36256,7 +36256,7 @@
           <t>F | 431呎 (2房)
 $791万
 $18,346/呎
-(26年-05月-05日)</t>
+(26年-05月-06日)</t>
         </is>
       </c>
     </row>
@@ -36279,7 +36279,7 @@
           <t>B | 695呎 (3房)
 $1631万
 $23,471/呎
-(26年-04月-26日)</t>
+(26年-04月-27日)</t>
         </is>
       </c>
       <c r="D13" s="22" t="inlineStr">
@@ -36311,7 +36311,7 @@
           <t>F | 431呎 (2房)
 $789万
 $18,302/呎
-(26年-05月-06日)</t>
+(26年-05月-07日)</t>
         </is>
       </c>
     </row>
@@ -36358,7 +36358,7 @@
           <t>E | 429呎 (2房)
 $800万
 $18,653/呎
-(26年-05月-05日)</t>
+(26年-05月-06日)</t>
         </is>
       </c>
       <c r="G14" s="20" t="inlineStr">
@@ -36366,7 +36366,7 @@
           <t>F | 431呎 (2房)
 $796万
 $18,459/呎
-(26年-05月-06日)</t>
+(26年-05月-07日)</t>
         </is>
       </c>
     </row>
@@ -36468,7 +36468,7 @@
           <t>E | 429呎 (2房)
 $794万
 $18,513/呎
-(26年-05月-07日)</t>
+(26年-05月-08日)</t>
         </is>
       </c>
       <c r="G16" s="20" t="inlineStr">
@@ -36476,7 +36476,7 @@
           <t>F | 431呎 (2房)
 $790万
 $18,323/呎
-(26年-05月-06日)</t>
+(26年-05月-07日)</t>
         </is>
       </c>
     </row>
@@ -36499,7 +36499,7 @@
           <t>B | 695呎 (3房)
 $1558万
 $22,416/呎
-(26年-01月-29日)</t>
+(26年-01月-30日)</t>
         </is>
       </c>
       <c r="D17" s="22" t="inlineStr">
@@ -36523,7 +36523,7 @@
           <t>E | 429呎 (2房)
 $792万
 $18,466/呎
-(26年-05月-06日)</t>
+(26年-05月-07日)</t>
         </is>
       </c>
       <c r="G17" s="20" t="inlineStr">
@@ -36531,7 +36531,7 @@
           <t>F | 431呎 (2房)
 $788万
 $18,276/呎
-(26年-05月-05日)</t>
+(26年-05月-06日)</t>
         </is>
       </c>
     </row>
@@ -36578,7 +36578,7 @@
           <t>E | 429呎 (2房)
 $790万
 $18,420/呎
-(26年-05月-06日)</t>
+(26年-05月-07日)</t>
         </is>
       </c>
       <c r="G18" s="20" t="inlineStr">
@@ -36586,7 +36586,7 @@
           <t>F | 431呎 (2房)
 $786万
 $18,230/呎
-(26年-05月-17日)</t>
+(26年-05月-18日)</t>
         </is>
       </c>
     </row>
@@ -36609,7 +36609,7 @@
           <t>B | 695呎 (3房)
 $1550万
 $22,304/呎
-(26年-02月-09日)</t>
+(26年-02月-10日)</t>
         </is>
       </c>
       <c r="D19" s="22" t="inlineStr">
@@ -36633,7 +36633,7 @@
           <t>E | 429呎 (2房)
 $788万
 $18,373/呎
-(26年-05月-06日)</t>
+(26年-05月-07日)</t>
         </is>
       </c>
       <c r="G19" s="20" t="inlineStr">
@@ -36641,7 +36641,7 @@
           <t>F | 431呎 (2房)
 $792万
 $18,387/呎
-(26年-05月-14日)</t>
+(26年-05月-15日)</t>
         </is>
       </c>
     </row>
@@ -36664,7 +36664,7 @@
           <t>B | 695呎 (3房)
 $1546万
 $22,249/呎
-(26年-02月-25日)</t>
+(26年-02月-26日)</t>
         </is>
       </c>
       <c r="D20" s="22" t="inlineStr">
@@ -36688,7 +36688,7 @@
           <t>E | 429呎 (2房)
 $786万
 $18,329/呎
-(26年-05月-06日)</t>
+(26年-05月-07日)</t>
         </is>
       </c>
       <c r="G20" s="20" t="inlineStr">
@@ -36696,7 +36696,7 @@
           <t>F | 431呎 (2房)
 $782万
 $18,139/呎
-(26年-05月-05日)</t>
+(26年-05月-06日)</t>
         </is>
       </c>
     </row>
@@ -36711,7 +36711,7 @@
           <t>A | 640呎 (3房)
 $1444万
 $22,564/呎
-(26年-05月-18日)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
       <c r="C21" s="20" t="inlineStr">
@@ -36719,7 +36719,7 @@
           <t>B | 695呎 (3房)
 $1542万
 $22,193/呎
-(26年-03月-02日)</t>
+(26年-03月-03日)</t>
         </is>
       </c>
       <c r="D21" s="22" t="inlineStr">
@@ -36743,7 +36743,7 @@
           <t>E | 429呎 (2房)
 $784万
 $18,282/呎
-(26年-05月-06日)</t>
+(26年-05月-07日)</t>
         </is>
       </c>
       <c r="G21" s="20" t="inlineStr">
@@ -36751,7 +36751,7 @@
           <t>F | 431呎 (2房)
 $780万
 $18,095/呎
-(26年-05月-05日)</t>
+(26年-05月-06日)</t>
         </is>
       </c>
     </row>
@@ -36766,7 +36766,7 @@
           <t>A | 640呎 (3房)
 $1432万
 $22,383/呎
-(26年-05月-05日)</t>
+(26年-05月-06日)</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
@@ -36774,7 +36774,7 @@
           <t>B | 695呎 (3房)
 $1556万
 $22,388/呎
-(26年-01月-20日)</t>
+(26年-01月-21日)</t>
         </is>
       </c>
       <c r="D22" s="22" t="inlineStr">
@@ -36798,7 +36798,7 @@
           <t>E | 429呎 (2房)
 $782万
 $18,238/呎
-(26年-05月-06日)</t>
+(26年-05月-07日)</t>
         </is>
       </c>
       <c r="G22" s="20" t="inlineStr">
@@ -36806,7 +36806,7 @@
           <t>F | 431呎 (2房)
 $769万
 $17,849/呎
-(26年-05月-05日)</t>
+(26年-05月-06日)</t>
         </is>
       </c>
     </row>
@@ -36821,7 +36821,7 @@
           <t>A | 640呎 (3房)
 $1429万
 $22,327/呎
-(26年-05月-06日)</t>
+(26年-05月-07日)</t>
         </is>
       </c>
       <c r="C23" s="20" t="inlineStr">
@@ -36829,7 +36829,7 @@
           <t>B | 695呎 (3房)
 $1604万
 $23,085/呎
-(26年-01月-07日)</t>
+(26年-01月-08日)</t>
         </is>
       </c>
       <c r="D23" s="22" t="inlineStr">
@@ -36853,7 +36853,7 @@
           <t>E | 429呎 (2房)
 $780万
 $18,191/呎
-(26年-05月-11日)</t>
+(26年-05月-12日)</t>
         </is>
       </c>
       <c r="G23" s="20" t="inlineStr">
@@ -36861,7 +36861,7 @@
           <t>F | 431呎 (2房)
 $776万
 $18,005/呎
-(26年-05月-12日)</t>
+(26年-05月-13日)</t>
         </is>
       </c>
     </row>
@@ -36876,7 +36876,7 @@
           <t>A | 640呎 (3房)
 $1433万
 $22,397/呎
-(26年-05月-20日)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
@@ -36884,7 +36884,7 @@
           <t>B | 695呎 (3房)
 $1531万
 $22,027/呎
-(26年-03月-03日)</t>
+(26年-03月-04日)</t>
         </is>
       </c>
       <c r="D24" s="22" t="inlineStr">
@@ -36908,7 +36908,7 @@
           <t>E | 429呎 (2房)
 $787万
 $18,350/呎
-(26年-05月-17日)</t>
+(26年-05月-18日)</t>
         </is>
       </c>
       <c r="G24" s="20" t="inlineStr">
@@ -36916,7 +36916,7 @@
           <t>F | 431呎 (2房)
 $729万
 $16,914/呎
-(26年-01月-05日)</t>
+(26年-01月-06日)</t>
         </is>
       </c>
     </row>
@@ -36931,7 +36931,7 @@
           <t>A | 640呎 (3房)
 $1426万
 $22,284/呎
-(26年-05月-17日)</t>
+(26年-05月-18日)</t>
         </is>
       </c>
       <c r="C25" s="20" t="inlineStr">
@@ -36939,7 +36939,7 @@
           <t>B | 695呎 (3房)
 $1523万
 $21,917/呎
-(26年-02月-22日)</t>
+(26年-02月-23日)</t>
         </is>
       </c>
       <c r="D25" s="22" t="inlineStr">
@@ -36963,7 +36963,7 @@
           <t>E | 429呎 (2房)
 $783万
 $18,259/呎
-(26年-05月-14日)</t>
+(26年-05月-15日)</t>
         </is>
       </c>
       <c r="G25" s="20" t="inlineStr">
@@ -36971,7 +36971,7 @@
           <t>F | 431呎 (2房)
 $725万
 $16,828/呎
-(26年-01月-07日)</t>
+(26年-01月-08日)</t>
         </is>
       </c>
     </row>
@@ -36986,7 +36986,7 @@
           <t>A | 640呎 (3房)
 $1415万
 $22,105/呎
-(26年-05月-06日)</t>
+(26年-05月-07日)</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
@@ -36994,7 +36994,7 @@
           <t>B | 695呎 (3房)
 $1520万
 $21,863/呎
-(26年-03月-01日)</t>
+(26年-03月-02日)</t>
         </is>
       </c>
       <c r="D26" s="22" t="inlineStr">
@@ -37018,7 +37018,7 @@
           <t>E | 429呎 (2房)
 $773万
 $18,012/呎
-(26年-05月-07日)</t>
+(26年-05月-08日)</t>
         </is>
       </c>
       <c r="G26" s="20" t="inlineStr">
@@ -37026,7 +37026,7 @@
           <t>F | 431呎 (2房)
 $724万
 $16,789/呎
-(26年-01月-07日)</t>
+(26年-01月-08日)</t>
         </is>
       </c>
     </row>
@@ -37041,7 +37041,7 @@
           <t>A | 640呎 (3房)
 $1357万
 $21,202/呎
-(26年-01月-13日)</t>
+(26年-01月-14日)</t>
         </is>
       </c>
       <c r="C27" s="20" t="inlineStr">
@@ -37049,7 +37049,7 @@
           <t>B | 695呎 (3房)
 $1516万
 $21,809/呎
-(26年-01月-08日)</t>
+(26年-01月-09日)</t>
         </is>
       </c>
       <c r="D27" s="22" t="inlineStr">
@@ -37073,7 +37073,7 @@
           <t>E | 429呎 (2房)
 $771万
 $17,967/呎
-(26年-05月-07日)</t>
+(26年-05月-08日)</t>
         </is>
       </c>
       <c r="G27" s="20" t="inlineStr">
@@ -37081,7 +37081,7 @@
           <t>F | 431呎 (2房)
 $722万
 $16,745/呎
-(26年-01月-05日)</t>
+(26年-01月-06日)</t>
         </is>
       </c>
     </row>
@@ -37096,7 +37096,7 @@
           <t>A | 640呎 (3房)
 $1416万
 $22,119/呎
-(26年-05月-20日)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="C28" s="20" t="inlineStr">
@@ -37104,7 +37104,7 @@
           <t>B | 695呎 (3房)
 $1512万
 $21,754/呎
-(26年-01月-08日)</t>
+(26年-01月-09日)</t>
         </is>
       </c>
       <c r="D28" s="22" t="inlineStr">
@@ -37128,7 +37128,7 @@
           <t>E | 429呎 (2房)
 $740万
 $17,261/呎
-(26年-01月-07日)</t>
+(26年-01月-08日)</t>
         </is>
       </c>
       <c r="G28" s="20" t="inlineStr">
@@ -37136,7 +37136,7 @@
           <t>F | 431呎 (2房)
 $720万
 $16,705/呎
-(26年-01月-06日)</t>
+(26年-01月-07日)</t>
         </is>
       </c>
     </row>
@@ -37151,7 +37151,7 @@
           <t>A | 640呎 (3房)
 $1404万
 $21,941/呎
-(26年-05月-07日)</t>
+(26年-05月-08日)</t>
         </is>
       </c>
       <c r="C29" s="20" t="inlineStr">
@@ -37159,7 +37159,7 @@
           <t>B | 695呎 (3房)
 $1508万
 $21,699/呎
-(26年-02月-24日)</t>
+(26年-02月-25日)</t>
         </is>
       </c>
       <c r="D29" s="22" t="inlineStr">
@@ -37183,7 +37183,7 @@
           <t>E | 429呎 (2房)
 $730万
 $17,026/呎
-(26年-01月-08日)</t>
+(26年-01月-09日)</t>
         </is>
       </c>
       <c r="G29" s="20" t="inlineStr">
@@ -37191,7 +37191,7 @@
           <t>F | 431呎 (2房)
 $718万
 $16,661/呎
-(26年-01月-01日)</t>
+(26年-01月-02日)</t>
         </is>
       </c>
     </row>
@@ -37206,7 +37206,7 @@
           <t>A | 640呎 (3房)
 $1401万
 $21,884/呎
-(26年-05月-12日)</t>
+(26年-05月-13日)</t>
         </is>
       </c>
       <c r="C30" s="20" t="inlineStr">
@@ -37214,7 +37214,7 @@
           <t>B | 695呎 (3房)
 $1522万
 $21,892/呎
-(26年-02月-25日)</t>
+(26年-02月-26日)</t>
         </is>
       </c>
       <c r="D30" s="22" t="inlineStr">
@@ -37238,7 +37238,7 @@
           <t>E | 429呎 (2房)
 $729万
 $16,984/呎
-(26年-01月-11日)</t>
+(26年-01月-12日)</t>
         </is>
       </c>
       <c r="G30" s="20" t="inlineStr">
@@ -37246,7 +37246,7 @@
           <t>F | 431呎 (2房)
 $716万
 $16,622/呎
-(26年-01月-06日)</t>
+(26年-01月-07日)</t>
         </is>
       </c>
     </row>
@@ -37261,7 +37261,7 @@
           <t>A | 640呎 (3房)
 $1397万
 $21,831/呎
-(26年-05月-05日)</t>
+(26年-05月-06日)</t>
         </is>
       </c>
       <c r="C31" s="20" t="inlineStr">
@@ -37269,7 +37269,7 @@
           <t>B | 695呎 (3房)
 $1501万
 $21,591/呎
-(26年-01月-13日)</t>
+(26年-01月-14日)</t>
         </is>
       </c>
       <c r="D31" s="22" t="inlineStr">
@@ -37293,7 +37293,7 @@
           <t>E | 429呎 (2房)
 $727万
 $16,942/呎
-(26年-01月-12日)</t>
+(26年-01月-13日)</t>
         </is>
       </c>
       <c r="G31" s="20" t="inlineStr">
@@ -37301,7 +37301,7 @@
           <t>F | 431呎 (2房)
 $750万
 $17,408/呎
-(26年-05月-18日)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
     </row>
@@ -37316,7 +37316,7 @@
           <t>A | 640呎 (3房)
 $1340万
 $20,939/呎
-(26年-01月-14日)</t>
+(26年-01月-15日)</t>
         </is>
       </c>
       <c r="C32" s="20" t="inlineStr">
@@ -37324,7 +37324,7 @@
           <t>B | 695呎 (3房)
 $1497万
 $21,538/呎
-(26年-01月-15日)</t>
+(26年-01月-16日)</t>
         </is>
       </c>
       <c r="D32" s="22" t="inlineStr">
@@ -37348,7 +37348,7 @@
           <t>E | 429呎 (2房)
 $725万
 $16,897/呎
-(26年-01月-11日)</t>
+(26年-01月-12日)</t>
         </is>
       </c>
       <c r="G32" s="20" t="inlineStr">
@@ -37356,7 +37356,7 @@
           <t>F | 431呎 (2房)
 $748万
 $17,367/呎
-(26年-05月-13日)</t>
+(26年-05月-14日)</t>
         </is>
       </c>
     </row>
@@ -37379,7 +37379,7 @@
           <t>B | 695呎 (3房)
 $1557万
 $22,404/呎
-(26年-04月-21日)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
       <c r="D33" s="22" t="inlineStr">
@@ -37403,7 +37403,7 @@
           <t>E | 429呎 (2房)
 $766万
 $17,853/呎
-(26年-05月-19日)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="G33" s="20" t="inlineStr">
@@ -37411,7 +37411,7 @@
           <t>F | 431呎 (2房)
 $753万
 $17,473/呎
-(26年-05月-18日)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
     </row>
@@ -37458,7 +37458,7 @@
           <t>E | 429呎 (2房)
 $756万
 $17,611/呎
-(26年-05月-11日)</t>
+(26年-05月-12日)</t>
         </is>
       </c>
       <c r="G34" s="20" t="inlineStr">
@@ -37466,7 +37466,7 @@
           <t>F | 431呎 (2房)
 $743万
 $17,234/呎
-(26年-05月-14日)</t>
+(26年-05月-15日)</t>
         </is>
       </c>
     </row>
@@ -38068,7 +38068,7 @@
           <t>C | 329呎 (1房)
 $639万
 $19,416/呎
-(26年-05月-18日)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
       <c r="E8" s="22" t="inlineStr">
@@ -38084,7 +38084,7 @@
           <t>E | 320呎 (1房)
 $622万
 $19,431/呎
-(26年-05月-14日)</t>
+(26年-05月-15日)</t>
         </is>
       </c>
       <c r="G8" s="20" t="inlineStr">
@@ -38092,7 +38092,7 @@
           <t>F | 320呎 (1房)
 $620万
 $19,369/呎
-(26年-05月-05日)</t>
+(26年-05月-06日)</t>
         </is>
       </c>
       <c r="H8" s="20" t="inlineStr">
@@ -38100,7 +38100,7 @@
           <t>G | 250呎 (开放式)
 $478万
 $19,136/呎
-(26年-05月-10日)</t>
+(26年-05月-11日)</t>
         </is>
       </c>
       <c r="I8" s="22" t="inlineStr">
@@ -38155,7 +38155,7 @@
           <t>C | 329呎 (1房)
 $637万
 $19,368/呎
-(26年-05月-20日)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="E9" s="22" t="inlineStr">
@@ -38171,7 +38171,7 @@
           <t>E | 320呎 (1房)
 $620万
 $19,384/呎
-(26年-05月-18日)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
       <c r="G9" s="20" t="inlineStr">
@@ -38179,7 +38179,7 @@
           <t>F | 320呎 (1房)
 $618万
 $19,319/呎
-(26年-05月-06日)</t>
+(26年-05月-07日)</t>
         </is>
       </c>
       <c r="H9" s="20" t="inlineStr">
@@ -38187,7 +38187,7 @@
           <t>G | 250呎 (开放式)
 $477万
 $19,092/呎
-(26年-05月-10日)</t>
+(26年-05月-11日)</t>
         </is>
       </c>
       <c r="I9" s="22" t="inlineStr">
@@ -38203,7 +38203,7 @@
           <t>J | 414呎 (2房)
 $829万
 $20,019/呎
-(26年-05月-12日)</t>
+(26年-05月-13日)</t>
         </is>
       </c>
       <c r="K9" s="22" t="inlineStr">
@@ -38242,7 +38242,7 @@
           <t>C | 329呎 (1房)
 $643万
 $19,535/呎
-(26年-05月-20日)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="E10" s="22" t="inlineStr">
@@ -38258,7 +38258,7 @@
           <t>E | 320呎 (1房)
 $619万
 $19,338/呎
-(26年-05月-18日)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
       <c r="G10" s="20" t="inlineStr">
@@ -38266,7 +38266,7 @@
           <t>F | 320呎 (1房)
 $622万
 $19,431/呎
-(26年-05月-14日)</t>
+(26年-05月-15日)</t>
         </is>
       </c>
       <c r="H10" s="20" t="inlineStr">
@@ -38274,7 +38274,7 @@
           <t>G | 250呎 (开放式)
 $482万
 $19,260/呎
-(26年-05月-19日)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="I10" s="22" t="inlineStr">
@@ -38290,7 +38290,7 @@
           <t>J | 414呎 (2房)
 $836万
 $20,196/呎
-(26年-05月-20日)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="K10" s="22" t="inlineStr">
@@ -38329,7 +38329,7 @@
           <t>C | 329呎 (1房)
 $629万
 $19,109/呎
-(26年-05月-06日)</t>
+(26年-05月-07日)</t>
         </is>
       </c>
       <c r="E11" s="22" t="inlineStr">
@@ -38345,7 +38345,7 @@
           <t>E | 320呎 (1房)
 $617万
 $19,291/呎
-(26年-05月-18日)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
       <c r="G11" s="20" t="inlineStr">
@@ -38353,7 +38353,7 @@
           <t>F | 320呎 (1房)
 $622万
 $19,438/呎
-(26年-04月-09日)</t>
+(26年-04月-10日)</t>
         </is>
       </c>
       <c r="H11" s="20" t="inlineStr">
@@ -38361,7 +38361,7 @@
           <t>G | 250呎 (开放式)
 $475万
 $18,996/呎
-(26年-05月-06日)</t>
+(26年-05月-07日)</t>
         </is>
       </c>
       <c r="I11" s="22" t="inlineStr">
@@ -38377,7 +38377,7 @@
           <t>J | 414呎 (2房)
 $825万
 $19,920/呎
-(26年-05月-07日)</t>
+(26年-05月-08日)</t>
         </is>
       </c>
       <c r="K11" s="22" t="inlineStr">
@@ -38416,7 +38416,7 @@
           <t>C | 329呎 (1房)
 $627万
 $19,061/呎
-(26年-05月-07日)</t>
+(26年-05月-08日)</t>
         </is>
       </c>
       <c r="E12" s="22" t="inlineStr">
@@ -38432,7 +38432,7 @@
           <t>E | 320呎 (1房)
 $616万
 $19,241/呎
-(26年-05月-18日)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
       <c r="G12" s="20" t="inlineStr">
@@ -38440,7 +38440,7 @@
           <t>F | 320呎 (1房)
 $614万
 $19,175/呎
-(26年-05月-05日)</t>
+(26年-05月-06日)</t>
         </is>
       </c>
       <c r="H12" s="20" t="inlineStr">
@@ -38448,7 +38448,7 @@
           <t>G | 250呎 (开放式)
 $474万
 $18,948/呎
-(26年-05月-06日)</t>
+(26年-05月-07日)</t>
         </is>
       </c>
       <c r="I12" s="22" t="inlineStr">
@@ -38464,7 +38464,7 @@
           <t>J | 414呎 (2房)
 $823万
 $19,872/呎
-(26年-05月-06日)</t>
+(26年-05月-07日)</t>
         </is>
       </c>
       <c r="K12" s="22" t="inlineStr">
@@ -38503,7 +38503,7 @@
           <t>C | 329呎 (1房)
 $626万
 $19,015/呎
-(26年-05月-07日)</t>
+(26年-05月-08日)</t>
         </is>
       </c>
       <c r="E13" s="22" t="inlineStr">
@@ -38519,7 +38519,7 @@
           <t>E | 320呎 (1房)
 $613万
 $19,156/呎
-(26年-04月-28日)</t>
+(26年-04月-29日)</t>
         </is>
       </c>
       <c r="G13" s="20" t="inlineStr">
@@ -38527,7 +38527,7 @@
           <t>F | 320呎 (1房)
 $583万
 $18,219/呎
-(26年-03月-01日)</t>
+(26年-03月-02日)</t>
         </is>
       </c>
       <c r="H13" s="20" t="inlineStr">
@@ -38535,7 +38535,7 @@
           <t>G | 250呎 (开放式)
 $473万
 $18,904/呎
-(26年-05月-06日)</t>
+(26年-05月-07日)</t>
         </is>
       </c>
       <c r="I13" s="22" t="inlineStr">
@@ -38551,7 +38551,7 @@
           <t>J | 414呎 (2房)
 $820万
 $19,819/呎
-(26年-05月-06日)</t>
+(26年-05月-07日)</t>
         </is>
       </c>
       <c r="K13" s="22" t="inlineStr">
@@ -38582,7 +38582,7 @@
           <t>B | 454呎 (2房)
 $962万
 $21,198/呎
-(26年-05月-06日)</t>
+(26年-05月-07日)</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -38590,7 +38590,7 @@
           <t>C | 329呎 (1房)
 $624万
 $18,967/呎
-(26年-05月-06日)</t>
+(26年-05月-07日)</t>
         </is>
       </c>
       <c r="E14" s="22" t="inlineStr">
@@ -38606,7 +38606,7 @@
           <t>E | 320呎 (1房)
 $611万
 $19,106/呎
-(26年-05月-03日)</t>
+(26年-05月-04日)</t>
         </is>
       </c>
       <c r="G14" s="20" t="inlineStr">
@@ -38614,7 +38614,7 @@
           <t>F | 320呎 (1房)
 $582万
 $18,172/呎
-(26年-02月-22日)</t>
+(26年-02月-23日)</t>
         </is>
       </c>
       <c r="H14" s="20" t="inlineStr">
@@ -38622,7 +38622,7 @@
           <t>G | 250呎 (开放式)
 $471万
 $18,852/呎
-(26年-05月-07日)</t>
+(26年-05月-08日)</t>
         </is>
       </c>
       <c r="I14" s="22" t="inlineStr">
@@ -38638,7 +38638,7 @@
           <t>J | 414呎 (2房)
 $818万
 $19,771/呎
-(26年-05月-11日)</t>
+(26年-05月-12日)</t>
         </is>
       </c>
       <c r="K14" s="22" t="inlineStr">
@@ -38756,7 +38756,7 @@
           <t>B | 454呎 (2房)
 $955万
 $21,040/呎
-(26年-05月-07日)</t>
+(26年-05月-08日)</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -38764,7 +38764,7 @@
           <t>C | 329呎 (1房)
 $619万
 $18,827/呎
-(26年-05月-06日)</t>
+(26年-05月-07日)</t>
         </is>
       </c>
       <c r="E16" s="22" t="inlineStr">
@@ -38780,7 +38780,7 @@
           <t>E | 320呎 (1房)
 $607万
 $18,966/呎
-(26年-05月-03日)</t>
+(26年-05月-04日)</t>
         </is>
       </c>
       <c r="G16" s="20" t="inlineStr">
@@ -38788,7 +38788,7 @@
           <t>F | 320呎 (1房)
 $577万
 $18,038/呎
-(26年-02月-25日)</t>
+(26年-02月-26日)</t>
         </is>
       </c>
       <c r="H16" s="20" t="inlineStr">
@@ -38796,7 +38796,7 @@
           <t>G | 250呎 (开放式)
 $468万
 $18,712/呎
-(26年-05月-11日)</t>
+(26年-05月-12日)</t>
         </is>
       </c>
       <c r="I16" s="22" t="inlineStr">
@@ -38812,7 +38812,7 @@
           <t>J | 414呎 (2房)
 $812万
 $19,623/呎
-(26年-05月-06日)</t>
+(26年-05月-07日)</t>
         </is>
       </c>
       <c r="K16" s="22" t="inlineStr">
@@ -38843,7 +38843,7 @@
           <t>B | 454呎 (2房)
 $953万
 $20,987/呎
-(26年-05月-12日)</t>
+(26年-05月-13日)</t>
         </is>
       </c>
       <c r="D17" s="20" t="inlineStr">
@@ -38851,7 +38851,7 @@
           <t>C | 329呎 (1房)
 $618万
 $18,781/呎
-(26年-05月-06日)</t>
+(26年-05月-07日)</t>
         </is>
       </c>
       <c r="E17" s="22" t="inlineStr">
@@ -38867,7 +38867,7 @@
           <t>E | 320呎 (1房)
 $579万
 $18,106/呎
-(26年-02月-23日)</t>
+(26年-02月-24日)</t>
         </is>
       </c>
       <c r="G17" s="20" t="inlineStr">
@@ -38875,7 +38875,7 @@
           <t>F | 320呎 (1房)
 $576万
 $17,991/呎
-(26年-02月-24日)</t>
+(26年-02月-25日)</t>
         </is>
       </c>
       <c r="H17" s="20" t="inlineStr">
@@ -38883,7 +38883,7 @@
           <t>G | 250呎 (开放式)
 $467万
 $18,668/呎
-(26年-05月-17日)</t>
+(26年-05月-18日)</t>
         </is>
       </c>
       <c r="I17" s="22" t="inlineStr">
@@ -38899,7 +38899,7 @@
           <t>J | 414呎 (2房)
 $810万
 $19,575/呎
-(26年-05月-06日)</t>
+(26年-05月-07日)</t>
         </is>
       </c>
       <c r="K17" s="22" t="inlineStr">
@@ -38930,7 +38930,7 @@
           <t>B | 454呎 (2房)
 $961万
 $21,172/呎
-(26年-05月-18日)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -38938,7 +38938,7 @@
           <t>C | 329呎 (1房)
 $616万
 $18,733/呎
-(26年-05月-06日)</t>
+(26年-05月-07日)</t>
         </is>
       </c>
       <c r="E18" s="22" t="inlineStr">
@@ -38954,7 +38954,7 @@
           <t>E | 320呎 (1房)
 $604万
 $18,872/呎
-(26年-04月-28日)</t>
+(26年-04月-29日)</t>
         </is>
       </c>
       <c r="G18" s="20" t="inlineStr">
@@ -38962,7 +38962,7 @@
           <t>F | 320呎 (1房)
 $574万
 $17,944/呎
-(26年-02月-12日)</t>
+(26年-02月-13日)</t>
         </is>
       </c>
       <c r="H18" s="20" t="inlineStr">
@@ -38970,7 +38970,7 @@
           <t>G | 250呎 (开放式)
 $471万
 $18,828/呎
-(26年-05月-14日)</t>
+(26年-05月-15日)</t>
         </is>
       </c>
       <c r="I18" s="22" t="inlineStr">
@@ -38986,7 +38986,7 @@
           <t>J | 414呎 (2房)
 $817万
 $19,744/呎
-(26年-05月-11日)</t>
+(26年-05月-12日)</t>
         </is>
       </c>
       <c r="K18" s="22" t="inlineStr">
@@ -39017,7 +39017,7 @@
           <t>B | 454呎 (2房)
 $959万
 $21,117/呎
-(26年-05月-17日)</t>
+(26年-05月-18日)</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr">
@@ -39025,7 +39025,7 @@
           <t>C | 329呎 (1房)
 $615万
 $18,687/呎
-(26年-05月-06日)</t>
+(26年-05月-07日)</t>
         </is>
       </c>
       <c r="E19" s="22" t="inlineStr">
@@ -39041,7 +39041,7 @@
           <t>E | 320呎 (1房)
 $602万
 $18,825/呎
-(26年-05月-03日)</t>
+(26年-05月-04日)</t>
         </is>
       </c>
       <c r="G19" s="20" t="inlineStr">
@@ -39049,7 +39049,7 @@
           <t>F | 320呎 (1房)
 $573万
 $17,900/呎
-(26年-02月-04日)</t>
+(26年-02月-05日)</t>
         </is>
       </c>
       <c r="H19" s="20" t="inlineStr">
@@ -39057,7 +39057,7 @@
           <t>G | 250呎 (开放式)
 $475万
 $18,992/呎
-(26年-05月-18日)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
       <c r="I19" s="22" t="inlineStr">
@@ -39073,7 +39073,7 @@
           <t>J | 414呎 (2房)
 $815万
 $19,696/呎
-(26年-05月-18日)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
       <c r="K19" s="22" t="inlineStr">
@@ -39104,7 +39104,7 @@
           <t>B | 454呎 (2房)
 $946万
 $20,830/呎
-(26年-05月-07日)</t>
+(26年-05月-08日)</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
@@ -39112,7 +39112,7 @@
           <t>C | 329呎 (1房)
 $613万
 $18,641/呎
-(26年-05月-06日)</t>
+(26年-05月-07日)</t>
         </is>
       </c>
       <c r="E20" s="22" t="inlineStr">
@@ -39128,7 +39128,7 @@
           <t>E | 320呎 (1房)
 $601万
 $18,775/呎
-(26年-05月-03日)</t>
+(26年-05月-04日)</t>
         </is>
       </c>
       <c r="G20" s="20" t="inlineStr">
@@ -39136,7 +39136,7 @@
           <t>F | 320呎 (1房)
 $571万
 $17,856/呎
-(26年-02月-01日)</t>
+(26年-02月-02日)</t>
         </is>
       </c>
       <c r="H20" s="20" t="inlineStr">
@@ -39144,7 +39144,7 @@
           <t>G | 250呎 (开放式)
 $468万
 $18,736/呎
-(26年-05月-07日)</t>
+(26年-05月-08日)</t>
         </is>
       </c>
       <c r="I20" s="22" t="inlineStr">
@@ -39160,7 +39160,7 @@
           <t>J | 414呎 (2房)
 $804万
 $19,428/呎
-(26年-05月-07日)</t>
+(26年-05月-08日)</t>
         </is>
       </c>
       <c r="K20" s="22" t="inlineStr">
@@ -39191,7 +39191,7 @@
           <t>B | 454呎 (2房)
 $943万
 $20,780/呎
-(26年-05月-07日)</t>
+(26年-05月-08日)</t>
         </is>
       </c>
       <c r="D21" s="20" t="inlineStr">
@@ -39199,7 +39199,7 @@
           <t>C | 329呎 (1房)
 $612万
 $18,593/呎
-(26年-05月-06日)</t>
+(26年-05月-07日)</t>
         </is>
       </c>
       <c r="E21" s="22" t="inlineStr">
@@ -39215,7 +39215,7 @@
           <t>E | 320呎 (1房)
 $599万
 $18,728/呎
-(26年-05月-03日)</t>
+(26年-05月-04日)</t>
         </is>
       </c>
       <c r="G21" s="20" t="inlineStr">
@@ -39223,7 +39223,7 @@
           <t>F | 320呎 (1房)
 $570万
 $17,812/呎
-(26年-01月-22日)</t>
+(26年-01月-23日)</t>
         </is>
       </c>
       <c r="H21" s="20" t="inlineStr">
@@ -39231,7 +39231,7 @@
           <t>G | 250呎 (开放式)
 $462万
 $18,480/呎
-(26年-05月-10日)</t>
+(26年-05月-11日)</t>
         </is>
       </c>
       <c r="I21" s="22" t="inlineStr">
@@ -39247,7 +39247,7 @@
           <t>J | 414呎 (2房)
 $811万
 $19,599/呎
-(26年-05月-12日)</t>
+(26年-05月-13日)</t>
         </is>
       </c>
       <c r="K21" s="22" t="inlineStr">
@@ -39278,7 +39278,7 @@
           <t>B | 454呎 (2房)
 $923万
 $20,322/呎
-(26年-03月-02日)</t>
+(26年-03月-03日)</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
@@ -39286,7 +39286,7 @@
           <t>C | 329呎 (1房)
 $610万
 $18,547/呎
-(26年-05月-06日)</t>
+(26年-05月-07日)</t>
         </is>
       </c>
       <c r="E22" s="22" t="inlineStr">
@@ -39302,7 +39302,7 @@
           <t>E | 320呎 (1房)
 $566万
 $17,678/呎
-(26年-02月-12日)</t>
+(26年-02月-13日)</t>
         </is>
       </c>
       <c r="G22" s="20" t="inlineStr">
@@ -39310,7 +39310,7 @@
           <t>F | 320呎 (1房)
 $568万
 $17,766/呎
-(26年-02月-03日)</t>
+(26年-02月-04日)</t>
         </is>
       </c>
       <c r="H22" s="20" t="inlineStr">
@@ -39318,7 +39318,7 @@
           <t>G | 250呎 (开放式)
 $461万
 $18,436/呎
-(26年-05月-07日)</t>
+(26年-05月-08日)</t>
         </is>
       </c>
       <c r="I22" s="22" t="inlineStr">
@@ -39334,7 +39334,7 @@
           <t>J | 414呎 (2房)
 $800万
 $19,331/呎
-(26年-05月-10日)</t>
+(26年-05月-11日)</t>
         </is>
       </c>
       <c r="K22" s="22" t="inlineStr">
@@ -39365,7 +39365,7 @@
           <t>B | 454呎 (2房)
 $931万
 $20,500/呎
-(26年-03月-04日)</t>
+(26年-03月-05日)</t>
         </is>
       </c>
       <c r="D23" s="20" t="inlineStr">
@@ -39373,7 +39373,7 @@
           <t>C | 329呎 (1房)
 $609万
 $18,498/呎
-(26年-05月-06日)</t>
+(26年-05月-07日)</t>
         </is>
       </c>
       <c r="E23" s="22" t="inlineStr">
@@ -39389,7 +39389,7 @@
           <t>E | 320呎 (1房)
 $564万
 $17,634/呎
-(26年-01月-07日)</t>
+(26年-01月-08日)</t>
         </is>
       </c>
       <c r="G23" s="20" t="inlineStr">
@@ -39397,7 +39397,7 @@
           <t>F | 320呎 (1房)
 $567万
 $17,722/呎
-(26年-02月-05日)</t>
+(26年-02月-06日)</t>
         </is>
       </c>
       <c r="H23" s="20" t="inlineStr">
@@ -39405,7 +39405,7 @@
           <t>G | 250呎 (开放式)
 $465万
 $18,596/呎
-(26年-05月-06日)</t>
+(26年-05月-07日)</t>
         </is>
       </c>
       <c r="I23" s="22" t="inlineStr">
@@ -39421,7 +39421,7 @@
           <t>J | 414呎 (2房)
 $798万
 $19,285/呎
-(26年-05月-05日)</t>
+(26年-05月-06日)</t>
         </is>
       </c>
       <c r="K23" s="22" t="inlineStr">
@@ -39452,7 +39452,7 @@
           <t>B | 454呎 (2房)
 $918万
 $20,220/呎
-(26年-02月-25日)</t>
+(26年-02月-26日)</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
@@ -39460,7 +39460,7 @@
           <t>C | 329呎 (1房)
 $607万
 $18,453/呎
-(26年-05月-05日)</t>
+(26年-05月-06日)</t>
         </is>
       </c>
       <c r="E24" s="22" t="inlineStr">
@@ -39476,7 +39476,7 @@
           <t>E | 320呎 (1房)
 $563万
 $17,591/呎
-(26年-01月-12日)</t>
+(26年-01月-13日)</t>
         </is>
       </c>
       <c r="G24" s="20" t="inlineStr">
@@ -39484,7 +39484,7 @@
           <t>F | 320呎 (1房)
 $566万
 $17,678/呎
-(26年-02月-05日)</t>
+(26年-02月-06日)</t>
         </is>
       </c>
       <c r="H24" s="20" t="inlineStr">
@@ -39492,7 +39492,7 @@
           <t>G | 250呎 (开放式)
 $459万
 $18,344/呎
-(26年-05月-05日)</t>
+(26年-05月-06日)</t>
         </is>
       </c>
       <c r="I24" s="22" t="inlineStr">
@@ -39508,7 +39508,7 @@
           <t>J | 414呎 (2房)
 $796万
 $19,234/呎
-(26年-05月-14日)</t>
+(26年-05月-15日)</t>
         </is>
       </c>
       <c r="K24" s="22" t="inlineStr">
@@ -39539,7 +39539,7 @@
           <t>B | 454呎 (2房)
 $913万
 $20,119/呎
-(26年-03月-01日)</t>
+(26年-03月-02日)</t>
         </is>
       </c>
       <c r="D25" s="20" t="inlineStr">
@@ -39547,7 +39547,7 @@
           <t>C | 329呎 (1房)
 $604万
 $18,362/呎
-(26年-05月-06日)</t>
+(26年-05月-07日)</t>
         </is>
       </c>
       <c r="E25" s="22" t="inlineStr">
@@ -39563,7 +39563,7 @@
           <t>E | 320呎 (1房)
 $560万
 $17,503/呎
-(26年-01月-08日)</t>
+(26年-01月-09日)</t>
         </is>
       </c>
       <c r="G25" s="20" t="inlineStr">
@@ -39571,7 +39571,7 @@
           <t>F | 320呎 (1房)
 $563万
 $17,591/呎
-(26年-02月-15日)</t>
+(26年-02月-16日)</t>
         </is>
       </c>
       <c r="H25" s="20" t="inlineStr">
@@ -39579,7 +39579,7 @@
           <t>G | 250呎 (开放式)
 $426万
 $17,056/呎
-(26年-01月-08日)</t>
+(26年-01月-09日)</t>
         </is>
       </c>
       <c r="I25" s="22" t="inlineStr">
@@ -39595,7 +39595,7 @@
           <t>J | 414呎 (2房)
 $792万
 $19,140/呎
-(26年-05月-07日)</t>
+(26年-05月-08日)</t>
         </is>
       </c>
       <c r="K25" s="22" t="inlineStr">
@@ -39626,7 +39626,7 @@
           <t>B | 454呎 (2房)
 $911万
 $20,068/呎
-(26年-02月-10日)</t>
+(26年-02月-11日)</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
@@ -39634,7 +39634,7 @@
           <t>C | 329呎 (1房)
 $603万
 $18,319/呎
-(26年-05月-06日)</t>
+(26年-05月-07日)</t>
         </is>
       </c>
       <c r="E26" s="22" t="inlineStr">
@@ -39650,7 +39650,7 @@
           <t>E | 320呎 (1房)
 $559万
 $17,462/呎
-(26年-01月-08日)</t>
+(26年-01月-09日)</t>
         </is>
       </c>
       <c r="G26" s="20" t="inlineStr">
@@ -39658,7 +39658,7 @@
           <t>F | 320呎 (1房)
 $562万
 $17,547/呎
-(26年-02月-05日)</t>
+(26年-02月-06日)</t>
         </is>
       </c>
       <c r="H26" s="20" t="inlineStr">
@@ -39666,7 +39666,7 @@
           <t>G | 250呎 (开放式)
 $425万
 $17,016/呎
-(26年-01月-08日)</t>
+(26年-01月-09日)</t>
         </is>
       </c>
       <c r="I26" s="22" t="inlineStr">
@@ -39682,7 +39682,7 @@
           <t>J | 414呎 (2房)
 $790万
 $19,094/呎
-(26年-05月-05日)</t>
+(26年-05月-06日)</t>
         </is>
       </c>
       <c r="K26" s="22" t="inlineStr">
@@ -39713,7 +39713,7 @@
           <t>B | 454呎 (2房)
 $909万
 $20,018/呎
-(26年-02月-04日)</t>
+(26年-02月-05日)</t>
         </is>
       </c>
       <c r="D27" s="20" t="inlineStr">
@@ -39721,7 +39721,7 @@
           <t>C | 329呎 (1房)
 $601万
 $18,274/呎
-(26年-05月-06日)</t>
+(26年-05月-07日)</t>
         </is>
       </c>
       <c r="E27" s="22" t="inlineStr">
@@ -39737,7 +39737,7 @@
           <t>E | 320呎 (1房)
 $557万
 $17,419/呎
-(26年-01月-08日)</t>
+(26年-01月-09日)</t>
         </is>
       </c>
       <c r="G27" s="20" t="inlineStr">
@@ -39745,7 +39745,7 @@
           <t>F | 320呎 (1房)
 $560万
 $17,503/呎
-(26年-01月-25日)</t>
+(26年-01月-26日)</t>
         </is>
       </c>
       <c r="H27" s="20" t="inlineStr">
@@ -39753,7 +39753,7 @@
           <t>G | 250呎 (开放式)
 $424万
 $16,972/呎
-(26年-01月-13日)</t>
+(26年-01月-14日)</t>
         </is>
       </c>
       <c r="I27" s="22" t="inlineStr">
@@ -39769,7 +39769,7 @@
           <t>J | 414呎 (2房)
 $744万
 $17,966/呎
-(26年-01月-13日)</t>
+(26年-01月-14日)</t>
         </is>
       </c>
       <c r="K27" s="22" t="inlineStr">
@@ -39800,7 +39800,7 @@
           <t>B | 454呎 (2房)
 $906万
 $19,967/呎
-(26年-03月-01日)</t>
+(26年-03月-02日)</t>
         </is>
       </c>
       <c r="D28" s="20" t="inlineStr">
@@ -39808,7 +39808,7 @@
           <t>C | 329呎 (1房)
 $606万
 $18,432/呎
-(26年-05月-07日)</t>
+(26年-05月-08日)</t>
         </is>
       </c>
       <c r="E28" s="22" t="inlineStr">
@@ -39824,7 +39824,7 @@
           <t>E | 320呎 (1房)
 $556万
 $17,372/呎
-(26年-01月-11日)</t>
+(26年-01月-12日)</t>
         </is>
       </c>
       <c r="G28" s="20" t="inlineStr">
@@ -39832,7 +39832,7 @@
           <t>F | 320呎 (1房)
 $559万
 $17,459/呎
-(26年-02月-12日)</t>
+(26年-02月-13日)</t>
         </is>
       </c>
       <c r="H28" s="20" t="inlineStr">
@@ -39840,7 +39840,7 @@
           <t>G | 250呎 (开放式)
 $442万
 $17,700/呎
-(26年-01月-08日)</t>
+(26年-01月-09日)</t>
         </is>
       </c>
       <c r="I28" s="22" t="inlineStr">
@@ -39856,7 +39856,7 @@
           <t>J | 414呎 (2房)
 $776万
 $18,737/呎
-(26年-01月-08日)</t>
+(26年-01月-09日)</t>
         </is>
       </c>
       <c r="K28" s="22" t="inlineStr">
@@ -39887,7 +39887,7 @@
           <t>B | 454呎 (2房)
 $904万
 $19,919/呎
-(26年-03月-01日)</t>
+(26年-03月-02日)</t>
         </is>
       </c>
       <c r="D29" s="20" t="inlineStr">
@@ -39895,7 +39895,7 @@
           <t>C | 329呎 (1房)
 $598万
 $18,179/呎
-(26年-05月-06日)</t>
+(26年-05月-07日)</t>
         </is>
       </c>
       <c r="E29" s="22" t="inlineStr">
@@ -39911,7 +39911,7 @@
           <t>E | 320呎 (1房)
 $554万
 $17,328/呎
-(26年-01月-08日)</t>
+(26年-01月-09日)</t>
         </is>
       </c>
       <c r="G29" s="20" t="inlineStr">
@@ -39919,7 +39919,7 @@
           <t>F | 320呎 (1房)
 $557万
 $17,419/呎
-(26年-02月-12日)</t>
+(26年-02月-13日)</t>
         </is>
       </c>
       <c r="H29" s="20" t="inlineStr">
@@ -39927,7 +39927,7 @@
           <t>G | 250呎 (开放式)
 $422万
 $16,888/呎
-(26年-01月-08日)</t>
+(26年-01月-09日)</t>
         </is>
       </c>
       <c r="I29" s="22" t="inlineStr">
@@ -39943,7 +39943,7 @@
           <t>J | 414呎 (2房)
 $774万
 $18,691/呎
-(26年-01月-08日)</t>
+(26年-01月-09日)</t>
         </is>
       </c>
       <c r="K29" s="22" t="inlineStr">
@@ -39974,7 +39974,7 @@
           <t>B | 454呎 (2房)
 $902万
 $19,868/呎
-(26年-01月-13日)</t>
+(26年-01月-14日)</t>
         </is>
       </c>
       <c r="D30" s="20" t="inlineStr">
@@ -39982,7 +39982,7 @@
           <t>C | 329呎 (1房)
 $597万
 $18,134/呎
-(26年-05月-05日)</t>
+(26年-05月-06日)</t>
         </is>
       </c>
       <c r="E30" s="22" t="inlineStr">
@@ -39998,7 +39998,7 @@
           <t>E | 320呎 (1房)
 $553万
 $17,284/呎
-(26年-01月-18日)</t>
+(26年-01月-19日)</t>
         </is>
       </c>
       <c r="G30" s="20" t="inlineStr">
@@ -40006,7 +40006,7 @@
           <t>F | 320呎 (1房)
 $556万
 $17,372/呎
-(26年-02月-23日)</t>
+(26年-02月-24日)</t>
         </is>
       </c>
       <c r="H30" s="20" t="inlineStr">
@@ -40014,7 +40014,7 @@
           <t>G | 250呎 (开放式)
 $421万
 $16,844/呎
-(26年-01月-07日)</t>
+(26年-01月-08日)</t>
         </is>
       </c>
       <c r="I30" s="22" t="inlineStr">
@@ -40030,7 +40030,7 @@
           <t>J | 414呎 (2房)
 $738万
 $17,833/呎
-(26年-01月-06日)</t>
+(26年-01月-07日)</t>
         </is>
       </c>
       <c r="K30" s="22" t="inlineStr">
@@ -40061,7 +40061,7 @@
           <t>B | 454呎 (2房)
 $900万
 $19,819/呎
-(26年-02月-25日)</t>
+(26年-02月-26日)</t>
         </is>
       </c>
       <c r="D31" s="20" t="inlineStr">
@@ -40069,7 +40069,7 @@
           <t>C | 329呎 (1房)
 $595万
 $18,091/呎
-(26年-05月-05日)</t>
+(26年-05月-06日)</t>
         </is>
       </c>
       <c r="E31" s="22" t="inlineStr">
@@ -40085,7 +40085,7 @@
           <t>E | 320呎 (1房)
 $577万
 $18,028/呎
-(26年-01月-12日)</t>
+(26年-01月-13日)</t>
         </is>
       </c>
       <c r="G31" s="20" t="inlineStr">
@@ -40093,7 +40093,7 @@
           <t>F | 320呎 (1房)
 $561万
 $17,525/呎
-(26年-01月-25日)</t>
+(26年-01月-26日)</t>
         </is>
       </c>
       <c r="H31" s="20" t="inlineStr">
@@ -40101,7 +40101,7 @@
           <t>G | 250呎 (开放式)
 $420万
 $16,804/呎
-(26年-01月-08日)</t>
+(26年-01月-09日)</t>
         </is>
       </c>
       <c r="I31" s="22" t="inlineStr">
@@ -40117,7 +40117,7 @@
           <t>J | 414呎 (2房)
 $736万
 $17,787/呎
-(25年-12月-13日)</t>
+(25年-12月-14日)</t>
         </is>
       </c>
       <c r="K31" s="22" t="inlineStr">
@@ -40148,7 +40148,7 @@
           <t>B | 454呎 (2房)
 $908万
 $19,996/呎
-(26年-03月-15日)</t>
+(26年-03月-16日)</t>
         </is>
       </c>
       <c r="D32" s="20" t="inlineStr">
@@ -40156,7 +40156,7 @@
           <t>C | 329呎 (1房)
 $594万
 $18,046/呎
-(26年-05月-06日)</t>
+(26年-05月-07日)</t>
         </is>
       </c>
       <c r="E32" s="22" t="inlineStr">
@@ -40172,7 +40172,7 @@
           <t>E | 320呎 (1房)
 $582万
 $18,178/呎
-(26年-04月-22日)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="G32" s="20" t="inlineStr">
@@ -40180,7 +40180,7 @@
           <t>F | 320呎 (1房)
 $553万
 $17,284/呎
-(26年-02月-10日)</t>
+(26年-02月-11日)</t>
         </is>
       </c>
       <c r="H32" s="20" t="inlineStr">
@@ -40188,7 +40188,7 @@
           <t>G | 250呎 (开放式)
 $419万
 $16,764/呎
-(26年-01月-13日)</t>
+(26年-01月-14日)</t>
         </is>
       </c>
       <c r="I32" s="22" t="inlineStr">
@@ -40204,7 +40204,7 @@
           <t>J | 414呎 (2房)
 $735万
 $17,744/呎
-(26年-01月-06日)</t>
+(26年-01月-07日)</t>
         </is>
       </c>
       <c r="K32" s="22" t="inlineStr">
@@ -40235,7 +40235,7 @@
           <t>B | 454呎 (2房)
 $903万
 $19,894/呎
-(26年-03月-16日)</t>
+(26年-03月-17日)</t>
         </is>
       </c>
       <c r="D33" s="20" t="inlineStr">
@@ -40243,7 +40243,7 @@
           <t>C | 329呎 (1房)
 $596万
 $18,106/呎
-(26年-05月-18日)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
       <c r="E33" s="22" t="inlineStr">
@@ -40267,7 +40267,7 @@
           <t>F | 320呎 (1房)
 $548万
 $17,116/呎
-(26年-02月-24日)</t>
+(26年-02月-25日)</t>
         </is>
       </c>
       <c r="H33" s="20" t="inlineStr">
@@ -40275,7 +40275,7 @@
           <t>G | 250呎 (开放式)
 $451万
 $18,044/呎
-(26年-05月-14日)</t>
+(26年-05月-15日)</t>
         </is>
       </c>
       <c r="I33" s="22" t="inlineStr">
@@ -40291,7 +40291,7 @@
           <t>J | 414呎 (2房)
 $731万
 $17,657/呎
-(26年-01月-07日)</t>
+(26年-01月-08日)</t>
         </is>
       </c>
       <c r="K33" s="22" t="inlineStr">
@@ -40322,7 +40322,7 @@
           <t>B | 454呎 (2房)
 $919万
 $20,240/呎
-(26年-05月-17日)</t>
+(26年-05月-18日)</t>
         </is>
       </c>
       <c r="D34" s="20" t="inlineStr">
@@ -40330,7 +40330,7 @@
           <t>C | 329呎 (1房)
 $594万
 $18,061/呎
-(26年-05月-18日)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
       <c r="E34" s="22" t="inlineStr">
@@ -40346,7 +40346,7 @@
           <t>E | 320呎 (1房)
 $546万
 $17,075/呎
-(26年-01月-14日)</t>
+(26年-01月-15日)</t>
         </is>
       </c>
       <c r="G34" s="24" t="inlineStr">
@@ -40362,7 +40362,7 @@
           <t>G | 250呎 (开放式)
 $450万
 $18,000/呎
-(26年-05月-17日)</t>
+(26年-05月-18日)</t>
         </is>
       </c>
       <c r="I34" s="22" t="inlineStr">
@@ -40378,7 +40378,7 @@
           <t>J | 414呎 (2房)
 $782万
 $18,877/呎
-(26年-05月-17日)</t>
+(26年-05月-18日)</t>
         </is>
       </c>
       <c r="K34" s="22" t="inlineStr">
